--- a/docs/Result.xlsx
+++ b/docs/Result.xlsx
@@ -1,29 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView windowWidth="23040" windowHeight="8616"/>
   </bookViews>
   <sheets>
     <sheet name="Time collection" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Specifications</t>
+  </si>
   <si>
     <t>Output Format</t>
   </si>
   <si>
+    <t>PDF (s)</t>
+  </si>
+  <si>
+    <t>DOCX (s)</t>
+  </si>
+  <si>
+    <t>1 Page</t>
+  </si>
+  <si>
+    <t>5 Pages</t>
+  </si>
+  <si>
+    <t>10 Pages</t>
+  </si>
+  <si>
+    <t>123 Pages</t>
+  </si>
+  <si>
     <t>Local Mode (CPU: 6 cores, 12 threads)</t>
   </si>
   <si>
@@ -42,40 +61,38 @@
     <t>JSON-specific field</t>
   </si>
   <si>
-    <t>Option</t>
-  </si>
-  <si>
-    <t>1 Pages</t>
-  </si>
-  <si>
-    <t>2 Pages</t>
-  </si>
-  <si>
-    <t>5 Pages</t>
-  </si>
-  <si>
-    <t>123 Pages</t>
-  </si>
-  <si>
-    <t>Pages (s)</t>
-  </si>
-  <si>
-    <t>gg gpu</t>
-  </si>
-  <si>
-    <t>gg cpu</t>
+    <t>Google Colab CPU</t>
+  </si>
+  <si>
+    <t>Intel(R) Xeon(R) CPU @ 2.00GHz (2 cores, 4 threads), with AVX-512 for tensor-turbo</t>
+  </si>
+  <si>
+    <t>Google Colab GPU</t>
+  </si>
+  <si>
+    <t>GG Colab CPU + GPU NVIDIA T4 (VRAM 15GB)</t>
+  </si>
+  <si>
+    <t>Out of CUDA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -83,19 +100,381 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -105,42 +484,406 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -189,7 +932,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -224,7 +967,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -398,171 +1141,401 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8" customWidth="1"/>
+    <col min="2" max="2" width="37.6" customWidth="1"/>
+    <col min="3" max="3" width="18.5666666666667" customWidth="1"/>
+    <col min="4" max="4" width="11.9" customWidth="1"/>
+    <col min="5" max="5" width="12.1" customWidth="1"/>
+    <col min="6" max="6" width="12.4" customWidth="1"/>
+    <col min="7" max="7" width="14.1" customWidth="1"/>
+    <col min="8" max="8" width="11.6" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="5"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D8" s="13">
+        <v>86.887</v>
+      </c>
+      <c r="E8" s="13">
+        <v>349.808</v>
+      </c>
+      <c r="F8" s="13">
+        <v>506</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="13">
+        <v>0.039</v>
+      </c>
+      <c r="I8" s="13">
+        <v>9.061</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="11"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="D9" s="13">
+        <v>83.903</v>
+      </c>
+      <c r="E9" s="13">
+        <v>351.711</v>
+      </c>
+      <c r="F9" s="19">
+        <v>504.35</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="13">
+        <v>0.049</v>
+      </c>
+      <c r="I9" s="13">
+        <v>3.279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="11"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="13">
+        <v>90.853</v>
+      </c>
+      <c r="E10" s="13">
+        <v>362.963</v>
+      </c>
+      <c r="F10" s="13">
+        <v>516.622</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="13">
+        <v>6.582</v>
+      </c>
+      <c r="I10" s="13">
+        <v>14.147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="11"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="13">
+        <v>100.182</v>
+      </c>
+      <c r="E11" s="13">
+        <v>364.253</v>
+      </c>
+      <c r="F11" s="13">
+        <v>510.983</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="13">
+        <v>18.522</v>
+      </c>
+      <c r="I11" s="19">
+        <v>19.72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="11"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="13">
+        <v>88.269</v>
+      </c>
+      <c r="E12" s="13">
+        <v>364.202</v>
+      </c>
+      <c r="F12" s="13">
+        <v>515.784</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="13">
+        <v>2.969</v>
+      </c>
+      <c r="I12" s="13">
+        <v>9.061</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="13">
+        <v>1.009</v>
+      </c>
+      <c r="I13" s="13">
+        <v>3.313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="11"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="D14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="I14" s="13">
+        <v>3.963</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="11"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="D15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="13">
+        <v>17.283</v>
+      </c>
+      <c r="I15" s="13">
+        <v>17.764</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="11"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="D16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="13">
+        <v>21.916</v>
+      </c>
+      <c r="I16" s="13">
+        <v>16.295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="11"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="D17" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="13">
+        <v>19.473</v>
+      </c>
+      <c r="I17" s="13">
+        <v>17.739</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
     <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/Result.xlsx
+++ b/docs/Result.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Time collection" sheetId="1" r:id="rId1"/>
+    <sheet name="Resource" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
   <si>
     <t>Options</t>
   </si>
@@ -74,6 +75,33 @@
   </si>
   <si>
     <t>Out of CUDA</t>
+  </si>
+  <si>
+    <t>Recommendation</t>
+  </si>
+  <si>
+    <t>Reasons</t>
+  </si>
+  <si>
+    <t>VRAM Usage</t>
+  </si>
+  <si>
+    <t>GPU with 32 GB VRAM</t>
+  </si>
+  <si>
+    <t>1. Using Qwen2VL for detecting characters</t>
+  </si>
+  <si>
+    <t>7 GB</t>
+  </si>
+  <si>
+    <t>2. Using NanonetsOCR for dectecting layout</t>
+  </si>
+  <si>
+    <t>3. Processing a pdf page with complex layout</t>
+  </si>
+  <si>
+    <t>6 GB</t>
   </si>
 </sst>
 </file>
@@ -81,13 +109,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,8 +145,107 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -126,29 +253,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,104 +288,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -289,19 +310,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -313,163 +490,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,20 +556,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,22 +586,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,156 +616,164 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -761,27 +782,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -789,9 +819,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -814,7 +841,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -822,12 +848,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -887,6 +910,53 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>168275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>80010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>626110</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="168275" y="956310"/>
+          <a:ext cx="10828655" cy="2297430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1162,30 +1232,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="17" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="17"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="1"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1198,170 +1268,170 @@
       <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="5"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="5"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="7" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="10">
         <v>86.887</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="10">
         <v>349.808</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="10">
         <v>506</v>
       </c>
       <c r="G8" s="18"/>
-      <c r="H8" s="13">
+      <c r="H8" s="10">
         <v>0.039</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="10">
         <v>9.061</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="7" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="10">
         <v>83.903</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="10">
         <v>351.711</v>
       </c>
       <c r="F9" s="19">
         <v>504.35</v>
       </c>
       <c r="G9" s="18"/>
-      <c r="H9" s="13">
+      <c r="H9" s="10">
         <v>0.049</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="10">
         <v>3.279</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="11"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="10">
         <v>90.853</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="10">
         <v>362.963</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="10">
         <v>516.622</v>
       </c>
       <c r="G10" s="18"/>
-      <c r="H10" s="13">
+      <c r="H10" s="10">
         <v>6.582</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="10">
         <v>14.147</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="11"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="10">
         <v>100.182</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="10">
         <v>364.253</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="10">
         <v>510.983</v>
       </c>
       <c r="G11" s="18"/>
-      <c r="H11" s="13">
+      <c r="H11" s="10">
         <v>18.522</v>
       </c>
       <c r="I11" s="19">
@@ -1369,154 +1439,154 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="11"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="13"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="10">
         <v>88.269</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="10">
         <v>364.202</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="10">
         <v>515.784</v>
       </c>
       <c r="G12" s="18"/>
-      <c r="H12" s="13">
+      <c r="H12" s="10">
         <v>2.969</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="10">
         <v>9.061</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="13">
+      <c r="D13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="10">
         <v>1.009</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="10">
         <v>3.313</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="11"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="7" t="s">
+      <c r="A14" s="13"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="16" t="s">
+      <c r="D14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="17" t="s">
         <v>19</v>
       </c>
       <c r="H14" s="20">
         <v>0.03</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="10">
         <v>3.963</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="11"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="7" t="s">
+      <c r="A15" s="13"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="13">
+      <c r="D15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="10">
         <v>17.283</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="10">
         <v>17.764</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="11"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="7" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="13">
+      <c r="D16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="10">
         <v>21.916</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="10">
         <v>16.295</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="11"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="7" t="s">
+      <c r="A17" s="13"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="13">
+      <c r="D17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="10">
         <v>19.473</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="10">
         <v>17.739</v>
       </c>
     </row>
@@ -1538,4 +1608,65 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8" outlineLevelRow="3" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="36.9" customWidth="1"/>
+    <col min="2" max="2" width="50.3" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/Result.xlsx
+++ b/docs/Result.xlsx
@@ -1,29 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView windowWidth="23040" windowHeight="8616"/>
   </bookViews>
   <sheets>
     <sheet name="Time collection" sheetId="1" r:id="rId1"/>
+    <sheet name="Resource" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Specifications</t>
+  </si>
   <si>
     <t>Output Format</t>
   </si>
   <si>
+    <t>PDF (s)</t>
+  </si>
+  <si>
+    <t>DOCX (s)</t>
+  </si>
+  <si>
+    <t>1 Page</t>
+  </si>
+  <si>
+    <t>5 Pages</t>
+  </si>
+  <si>
+    <t>10 Pages</t>
+  </si>
+  <si>
+    <t>123 Pages</t>
+  </si>
+  <si>
     <t>Local Mode (CPU: 6 cores, 12 threads)</t>
   </si>
   <si>
@@ -42,40 +62,65 @@
     <t>JSON-specific field</t>
   </si>
   <si>
-    <t>Option</t>
-  </si>
-  <si>
-    <t>1 Pages</t>
-  </si>
-  <si>
-    <t>2 Pages</t>
-  </si>
-  <si>
-    <t>5 Pages</t>
-  </si>
-  <si>
-    <t>123 Pages</t>
-  </si>
-  <si>
-    <t>Pages (s)</t>
-  </si>
-  <si>
-    <t>gg gpu</t>
-  </si>
-  <si>
-    <t>gg cpu</t>
+    <t>Google Colab CPU</t>
+  </si>
+  <si>
+    <t>Intel(R) Xeon(R) CPU @ 2.00GHz (2 cores, 4 threads), with AVX-512 for tensor-turbo</t>
+  </si>
+  <si>
+    <t>Google Colab GPU</t>
+  </si>
+  <si>
+    <t>GG Colab CPU + GPU NVIDIA T4 (VRAM 15GB)</t>
+  </si>
+  <si>
+    <t>Out of CUDA</t>
+  </si>
+  <si>
+    <t>Recommendation</t>
+  </si>
+  <si>
+    <t>Reasons</t>
+  </si>
+  <si>
+    <t>VRAM Usage</t>
+  </si>
+  <si>
+    <t>GPU with 32 GB VRAM</t>
+  </si>
+  <si>
+    <t>1. Using Qwen2VL for detecting characters</t>
+  </si>
+  <si>
+    <t>7 GB</t>
+  </si>
+  <si>
+    <t>2. Using NanonetsOCR for dectecting layout</t>
+  </si>
+  <si>
+    <t>3. Processing a pdf page with complex layout</t>
+  </si>
+  <si>
+    <t>6 GB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.000_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -83,19 +128,374 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -105,45 +505,458 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>168275</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>80010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>626110</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="168275" y="956310"/>
+          <a:ext cx="10828655" cy="2297430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -189,7 +1002,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -224,7 +1037,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -398,171 +1211,462 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8" customWidth="1"/>
+    <col min="2" max="2" width="37.6" customWidth="1"/>
+    <col min="3" max="3" width="18.5666666666667" customWidth="1"/>
+    <col min="4" max="4" width="11.9" customWidth="1"/>
+    <col min="5" max="5" width="12.1" customWidth="1"/>
+    <col min="6" max="6" width="12.4" customWidth="1"/>
+    <col min="7" max="7" width="14.1" customWidth="1"/>
+    <col min="8" max="8" width="11.6" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="7"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="7"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="7"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="7"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D8" s="10">
+        <v>86.887</v>
+      </c>
+      <c r="E8" s="10">
+        <v>349.808</v>
+      </c>
+      <c r="F8" s="10">
+        <v>506</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="10">
+        <v>0.039</v>
+      </c>
+      <c r="I8" s="10">
+        <v>9.061</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="13"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="D9" s="10">
+        <v>83.903</v>
+      </c>
+      <c r="E9" s="10">
+        <v>351.711</v>
+      </c>
+      <c r="F9" s="19">
+        <v>504.35</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="10">
+        <v>0.049</v>
+      </c>
+      <c r="I9" s="10">
+        <v>3.279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="13"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="10">
+        <v>90.853</v>
+      </c>
+      <c r="E10" s="10">
+        <v>362.963</v>
+      </c>
+      <c r="F10" s="10">
+        <v>516.622</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="10">
+        <v>6.582</v>
+      </c>
+      <c r="I10" s="10">
+        <v>14.147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="13"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="10">
+        <v>100.182</v>
+      </c>
+      <c r="E11" s="10">
+        <v>364.253</v>
+      </c>
+      <c r="F11" s="10">
+        <v>510.983</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="10">
+        <v>18.522</v>
+      </c>
+      <c r="I11" s="19">
+        <v>19.72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="13"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="10">
+        <v>88.269</v>
+      </c>
+      <c r="E12" s="10">
+        <v>364.202</v>
+      </c>
+      <c r="F12" s="10">
+        <v>515.784</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="10">
+        <v>2.969</v>
+      </c>
+      <c r="I12" s="10">
+        <v>9.061</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="10">
+        <v>1.009</v>
+      </c>
+      <c r="I13" s="10">
+        <v>3.313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="13"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="D14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="I14" s="10">
+        <v>3.963</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="13"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="D15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="10">
+        <v>17.283</v>
+      </c>
+      <c r="I15" s="10">
+        <v>17.764</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="13"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="D16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="10">
+        <v>21.916</v>
+      </c>
+      <c r="I16" s="10">
+        <v>16.295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="13"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
+      <c r="D17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="10">
+        <v>19.473</v>
+      </c>
+      <c r="I17" s="10">
+        <v>17.739</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
     <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8" outlineLevelRow="3" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="36.9" customWidth="1"/>
+    <col min="2" max="2" width="50.3" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>